--- a/Prueba_Carga_Masiva_Casos_Mixtos.xlsx
+++ b/Prueba_Carga_Masiva_Casos_Mixtos.xlsx
@@ -1530,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1551,6 +1551,9 @@
       <c r="F1" t="str">
         <v>motor</v>
       </c>
+      <c r="G1" t="str">
+        <v>referencia_oem</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1571,6 +1574,9 @@
       <c r="F2" t="str">
         <v>1.8 16V</v>
       </c>
+      <c r="G2" t="str">
+        <v>04465-02220</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1591,6 +1597,9 @@
       <c r="F3" t="str">
         <v>1.5 16V</v>
       </c>
+      <c r="G3" t="str">
+        <v>04465-52220</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1614,7 +1623,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1630,7 +1639,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VERSION_PLANTILLA: 2.0.0</v>
+        <v>VERSION_PLANTILLA: 2.1.0</v>
       </c>
     </row>
     <row r="3">
